--- a/site_libs/records/GPA.xlsx
+++ b/site_libs/records/GPA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Portfolio\site_libs\records\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kctolli.github.io\site_libs\records\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9C5B21-7B5C-4A07-8D14-1AD41C94BEB9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4C7F10-E705-45D4-A02A-F5FDA2749241}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="287">
   <si>
     <t>Semesters</t>
   </si>
@@ -709,9 +709,6 @@
   </si>
   <si>
     <t>CSE 450</t>
-  </si>
-  <si>
-    <t>MATH 488</t>
   </si>
   <si>
     <t>ECEN MSE</t>
@@ -1723,11 +1720,11 @@
         <v>16</v>
       </c>
       <c r="B3" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A3,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A3,Semesters!$C$2:$C$45)</f>
         <v>13</v>
       </c>
       <c r="C3" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A3,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A3,Semesters!$E$2:$E$45)</f>
         <v>49.4</v>
       </c>
       <c r="D3" s="7">
@@ -1739,7 +1736,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A3,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A3,Semesters!$H$2:$H$45)</f>
         <v>36</v>
       </c>
       <c r="G3" s="7">
@@ -1781,11 +1778,11 @@
         <v>17</v>
       </c>
       <c r="B4" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A4,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A4,Semesters!$C$2:$C$45)</f>
         <v>14</v>
       </c>
       <c r="C4" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A4,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A4,Semesters!$E$2:$E$45)</f>
         <v>56</v>
       </c>
       <c r="D4" s="7">
@@ -1797,7 +1794,7 @@
         <v>9</v>
       </c>
       <c r="F4" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A4,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A4,Semesters!$H$2:$H$45)</f>
         <v>36</v>
       </c>
       <c r="G4" s="7">
@@ -1839,11 +1836,11 @@
         <v>18</v>
       </c>
       <c r="B5" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A5,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A5,Semesters!$C$2:$C$45)</f>
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A5,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A5,Semesters!$E$2:$E$45)</f>
         <v>8</v>
       </c>
       <c r="D5" s="7">
@@ -1855,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A5,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A5,Semesters!$H$2:$H$45)</f>
         <v>0</v>
       </c>
       <c r="G5" s="9">
@@ -1896,11 +1893,11 @@
         <v>19</v>
       </c>
       <c r="B6" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A6,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A6,Semesters!$C$2:$C$45)</f>
         <v>14.5</v>
       </c>
       <c r="C6" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A6,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A6,Semesters!$E$2:$E$45)</f>
         <v>56.2</v>
       </c>
       <c r="D6" s="7">
@@ -1912,7 +1909,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A6,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A6,Semesters!$H$2:$H$45)</f>
         <v>42.2</v>
       </c>
       <c r="G6" s="7">
@@ -1954,11 +1951,11 @@
         <v>20</v>
       </c>
       <c r="B7" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A7,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A7,Semesters!$C$2:$C$45)</f>
         <v>12.5</v>
       </c>
       <c r="C7" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A7,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A7,Semesters!$E$2:$E$45)</f>
         <v>43.7</v>
       </c>
       <c r="D7" s="7">
@@ -1970,7 +1967,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A7,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A7,Semesters!$H$2:$H$45)</f>
         <v>30</v>
       </c>
       <c r="G7" s="7">
@@ -2012,11 +2009,11 @@
         <v>21</v>
       </c>
       <c r="B8" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A8,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A8,Semesters!$C$2:$C$45)</f>
         <v>10</v>
       </c>
       <c r="C8" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A8,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A8,Semesters!$E$2:$E$45)</f>
         <v>35.200000000000003</v>
       </c>
       <c r="D8" s="7">
@@ -2028,7 +2025,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A8,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A8,Semesters!$H$2:$H$45)</f>
         <v>35.200000000000003</v>
       </c>
       <c r="G8" s="7">
@@ -2070,11 +2067,11 @@
         <v>22</v>
       </c>
       <c r="B9" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A9,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A9,Semesters!$C$2:$C$45)</f>
         <v>3</v>
       </c>
       <c r="C9" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A9,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A9,Semesters!$E$2:$E$45)</f>
         <v>10.199999999999999</v>
       </c>
       <c r="D9" s="7">
@@ -2085,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A9,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A9,Semesters!$H$2:$H$45)</f>
         <v>0</v>
       </c>
       <c r="G9" s="9">
@@ -2126,11 +2123,11 @@
         <v>23</v>
       </c>
       <c r="B10" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A10,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A10,Semesters!$C$2:$C$45)</f>
         <v>13</v>
       </c>
       <c r="C10" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A10,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A10,Semesters!$E$2:$E$45)</f>
         <v>37</v>
       </c>
       <c r="D10" s="7">
@@ -2142,7 +2139,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A10,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A10,Semesters!$H$2:$H$45)</f>
         <v>22.200000000000003</v>
       </c>
       <c r="G10" s="7">
@@ -2184,11 +2181,11 @@
         <v>24</v>
       </c>
       <c r="B11" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A11,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A11,Semesters!$C$2:$C$45)</f>
         <v>12</v>
       </c>
       <c r="C11" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A11,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A11,Semesters!$E$2:$E$45)</f>
         <v>45.300000000000004</v>
       </c>
       <c r="D11" s="7">
@@ -2200,7 +2197,7 @@
         <v>9</v>
       </c>
       <c r="F11" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A11,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A11,Semesters!$H$2:$H$45)</f>
         <v>34.200000000000003</v>
       </c>
       <c r="G11" s="7">
@@ -2242,11 +2239,11 @@
         <v>25</v>
       </c>
       <c r="B12" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A12,Semesters!$C$2:$C$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A12,Semesters!$C$2:$C$45)</f>
         <v>8</v>
       </c>
       <c r="C12" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A12,Semesters!$E$2:$E$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A12,Semesters!$E$2:$E$45)</f>
         <v>32</v>
       </c>
       <c r="D12" s="7">
@@ -2258,7 +2255,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$46,Overview!A12,Semesters!$H$2:$H$46)</f>
+        <f>SUMIF(Semesters!$A$2:$A$45,Overview!A12,Semesters!$H$2:$H$45)</f>
         <v>32</v>
       </c>
       <c r="G12" s="7">
@@ -2300,57 +2297,57 @@
         <v>26</v>
       </c>
       <c r="B13" s="2">
-        <f>SUMIF(Semesters!$A$2:$A$500,Overview!A13,Semesters!$C$2:$C$500)</f>
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="e">
-        <f>SUMIF(Semesters!$A$2:$A$500,Overview!A13,Semesters!$E$2:$E$500)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D13" s="12" t="e">
+        <f>SUMIF(Semesters!$A$2:$A$498,Overview!A13,Semesters!$C$2:$C$498)</f>
+        <v>6</v>
+      </c>
+      <c r="C13" s="2">
+        <f>SUMIF(Semesters!$A$2:$A$498,Overview!A13,Semesters!$E$2:$E$498)</f>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D13" s="12">
         <f t="shared" si="0"/>
-        <v>#N/A</v>
+        <v>3.4</v>
       </c>
       <c r="E13" s="2">
         <f>B13</f>
-        <v>10</v>
-      </c>
-      <c r="F13" s="2" t="e">
-        <f>SUMIF(Semesters!$A$2:$A$500,Overview!A13,Semesters!$H$2:$H$500)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G13" s="7" t="e">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2">
+        <f>SUMIF(Semesters!$A$2:$A$498,Overview!A13,Semesters!$H$2:$H$498)</f>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="G13" s="7">
         <f t="shared" si="12"/>
-        <v>#N/A</v>
+        <v>3.4</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2">
         <f t="shared" si="6"/>
-        <v>112</v>
-      </c>
-      <c r="J13" s="2" t="e">
+        <v>108</v>
+      </c>
+      <c r="J13" s="2">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K13" s="7" t="e">
+        <v>393.4</v>
+      </c>
+      <c r="K13" s="7">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>3.6425925925925924</v>
       </c>
       <c r="L13" s="2">
         <f t="shared" si="8"/>
-        <v>84</v>
-      </c>
-      <c r="M13" s="2" t="e">
+        <v>80</v>
+      </c>
+      <c r="M13" s="2">
         <f t="shared" si="9"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N13" s="7" t="e">
+        <v>288.19999999999993</v>
+      </c>
+      <c r="N13" s="7">
         <f t="shared" si="5"/>
-        <v>#N/A</v>
+        <v>3.6024999999999991</v>
       </c>
       <c r="O13" s="8">
         <f t="shared" si="10"/>
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6160,7 +6157,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6216,7 +6213,7 @@
         <v>194</v>
       </c>
       <c r="E2" s="6">
-        <f t="shared" ref="E2:E44" si="0">VLOOKUP(D2,$J$2:$K$15,2,FALSE)*C2</f>
+        <f t="shared" ref="E2:E43" si="0">VLOOKUP(D2,$J$2:$K$15,2,FALSE)*C2</f>
         <v>5.4</v>
       </c>
       <c r="F2" s="1"/>
@@ -6224,7 +6221,7 @@
         <v>30</v>
       </c>
       <c r="H2" s="6">
-        <f t="shared" ref="H2:H44" si="1">VLOOKUP(G2,$J$2:$K$15,2,FALSE)*C2</f>
+        <f t="shared" ref="H2:H43" si="1">VLOOKUP(G2,$J$2:$K$15,2,FALSE)*C2</f>
         <v>0</v>
       </c>
       <c r="I2" s="1"/>
@@ -7481,24 +7478,26 @@
         <v>26</v>
       </c>
       <c r="B44" s="56" t="s">
-        <v>60</v>
+        <v>218</v>
       </c>
       <c r="C44" s="56">
-        <v>1</v>
-      </c>
-      <c r="D44" s="56"/>
-      <c r="E44" s="6" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="56">
-        <f>D44</f>
-        <v>0</v>
-      </c>
-      <c r="H44" s="6" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>3</v>
+      </c>
+      <c r="D44" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="E44" s="11">
+        <f t="shared" ref="E44:E45" si="2">VLOOKUP(D44,$J$2:$K$15,2,FALSE)*C44</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F44" s="59"/>
+      <c r="G44" s="56" t="str">
+        <f t="shared" ref="G44:G45" si="3">D44</f>
+        <v>B+</v>
+      </c>
+      <c r="H44" s="11">
+        <f t="shared" ref="H44:H45" si="4">VLOOKUP(G44,$J$2:$K$15,2,FALSE)*C44</f>
+        <v>10.199999999999999</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -7509,84 +7508,33 @@
         <v>26</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C45" s="56">
         <v>3</v>
       </c>
-      <c r="D45" s="56"/>
-      <c r="E45" s="11" t="e">
-        <f t="shared" ref="E45:E47" si="2">VLOOKUP(D45,$J$2:$K$15,2,FALSE)*C45</f>
-        <v>#N/A</v>
+      <c r="D45" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="E45" s="11">
+        <f t="shared" si="2"/>
+        <v>10.199999999999999</v>
       </c>
       <c r="F45" s="59"/>
-      <c r="G45" s="56">
-        <f t="shared" ref="G45:G47" si="3">D45</f>
-        <v>0</v>
-      </c>
-      <c r="H45" s="11" t="e">
-        <f t="shared" ref="H45:H47" si="4">VLOOKUP(G45,$J$2:$K$15,2,FALSE)*C45</f>
-        <v>#N/A</v>
+      <c r="G45" s="56" t="str">
+        <f t="shared" si="3"/>
+        <v>B+</v>
+      </c>
+      <c r="H45" s="11">
+        <f t="shared" si="4"/>
+        <v>10.199999999999999</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="C46" s="56">
-        <v>3</v>
-      </c>
-      <c r="D46" s="56"/>
-      <c r="E46" s="11" t="e">
-        <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="F46" s="59"/>
-      <c r="G46" s="56">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="11" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" s="56" t="s">
-        <v>220</v>
-      </c>
-      <c r="C47" s="56">
-        <v>3</v>
-      </c>
-      <c r="D47" s="56"/>
-      <c r="E47" s="11" t="e">
-        <f>VLOOKUP(D47,$J$2:$K$15,2,FALSE)*C47</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F47" s="59"/>
-      <c r="G47" s="56">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H47" s="11" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:K1"/>
@@ -7620,7 +7568,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="93" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
@@ -7632,7 +7580,7 @@
       <c r="I1" s="94"/>
       <c r="J1" s="61"/>
       <c r="K1" s="95" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L1" s="94"/>
       <c r="M1" s="94"/>
@@ -7640,14 +7588,14 @@
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="96" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B2" s="94"/>
       <c r="C2" s="94"/>
       <c r="D2" s="94"/>
       <c r="E2" s="62"/>
       <c r="F2" s="96" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G2" s="94"/>
       <c r="H2" s="94"/>
@@ -7660,7 +7608,7 @@
         <v>523</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N2" s="64">
         <v>3</v>
@@ -7684,7 +7632,7 @@
         <v>551</v>
       </c>
       <c r="M3" s="63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N3" s="64">
         <v>3</v>
@@ -7708,7 +7656,7 @@
         <v>595</v>
       </c>
       <c r="M4" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N4" s="26">
         <v>1</v>
@@ -7716,14 +7664,14 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B5" s="94"/>
       <c r="C5" s="94"/>
       <c r="D5" s="94"/>
       <c r="E5" s="67"/>
       <c r="F5" s="97" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G5" s="94"/>
       <c r="H5" s="94"/>
@@ -7736,7 +7684,7 @@
         <v>620</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N5" s="64">
         <v>3</v>
@@ -7760,7 +7708,7 @@
         <v>621</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N6" s="64">
         <v>3</v>
@@ -7779,7 +7727,7 @@
         <v>692</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I7" s="25">
         <v>2</v>
@@ -7792,7 +7740,7 @@
         <v>625</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N7" s="64">
         <v>3</v>
@@ -7806,14 +7754,14 @@
         <v>692</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D8" s="25">
         <v>2</v>
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="97" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G8" s="94"/>
       <c r="H8" s="94"/>
@@ -7837,10 +7785,10 @@
         <v>139</v>
       </c>
       <c r="B9" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>235</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>236</v>
       </c>
       <c r="D9" s="26">
         <v>6</v>
@@ -7858,7 +7806,7 @@
         <v>629</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N9" s="64">
         <v>3</v>
@@ -7866,7 +7814,7 @@
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="97" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B10" s="94"/>
       <c r="C10" s="94"/>
@@ -7884,7 +7832,7 @@
         <v>678</v>
       </c>
       <c r="M10" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N10" s="26">
         <v>3</v>
@@ -7897,20 +7845,20 @@
       <c r="D11" s="94"/>
       <c r="E11" s="67"/>
       <c r="F11" s="98" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G11" s="94"/>
       <c r="H11" s="94"/>
       <c r="I11" s="94"/>
       <c r="J11" s="61"/>
       <c r="K11" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L11" s="69">
         <v>601</v>
       </c>
       <c r="M11" s="68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N11" s="69">
         <v>3</v>
@@ -7918,7 +7866,7 @@
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="97" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B12" s="94"/>
       <c r="C12" s="94"/>
@@ -7931,20 +7879,20 @@
         <v>521</v>
       </c>
       <c r="H12" s="63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I12" s="64">
         <v>3</v>
       </c>
       <c r="J12" s="61"/>
       <c r="K12" s="68" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L12" s="69">
         <v>581</v>
       </c>
       <c r="M12" s="68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N12" s="69">
         <v>3</v>
@@ -7963,7 +7911,7 @@
         <v>611</v>
       </c>
       <c r="H13" s="101" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I13" s="100">
         <v>3</v>
@@ -9022,14 +8970,14 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="93" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
       <c r="D1" s="94"/>
       <c r="E1" s="61"/>
       <c r="F1" s="95" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G1" s="94"/>
       <c r="H1" s="94"/>
@@ -9041,7 +8989,7 @@
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="102" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B2" s="94"/>
       <c r="C2" s="94"/>
@@ -9054,20 +9002,20 @@
         <v>523</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I2" s="64">
         <v>3</v>
       </c>
       <c r="J2" s="26"/>
       <c r="K2" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L2" s="69">
         <v>601</v>
       </c>
       <c r="M2" s="68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N2" s="69">
         <v>3</v>
@@ -9086,20 +9034,20 @@
         <v>526</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I3" s="26">
         <v>3</v>
       </c>
       <c r="J3" s="26"/>
       <c r="K3" s="68" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L3" s="69">
         <v>550</v>
       </c>
       <c r="M3" s="68" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N3" s="69">
         <v>3</v>
@@ -9118,20 +9066,20 @@
         <v>551</v>
       </c>
       <c r="H4" s="63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I4" s="64">
         <v>3</v>
       </c>
       <c r="J4" s="26"/>
       <c r="K4" s="68" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L4" s="69">
         <v>581</v>
       </c>
       <c r="M4" s="68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N4" s="69">
         <v>3</v>
@@ -9139,7 +9087,7 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="102" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B5" s="94"/>
       <c r="C5" s="94"/>
@@ -9152,20 +9100,20 @@
         <v>595</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I5" s="26">
         <v>1</v>
       </c>
       <c r="J5" s="26"/>
       <c r="K5" s="68" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L5" s="26">
         <v>529</v>
       </c>
       <c r="M5" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N5" s="26">
         <v>3</v>
@@ -9184,20 +9132,20 @@
         <v>620</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I6" s="64">
         <v>3</v>
       </c>
       <c r="J6" s="26"/>
       <c r="K6" s="68" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L6" s="69">
         <v>544</v>
       </c>
       <c r="M6" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N6" s="69">
         <v>3</v>
@@ -9216,20 +9164,20 @@
         <v>621</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I7" s="64">
         <v>3</v>
       </c>
       <c r="J7" s="26"/>
       <c r="K7" s="68" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L7" s="69">
         <v>548</v>
       </c>
       <c r="M7" s="68" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N7" s="69">
         <v>3</v>
@@ -9248,20 +9196,20 @@
         <v>625</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I8" s="64">
         <v>3</v>
       </c>
       <c r="J8" s="26"/>
       <c r="K8" s="68" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L8" s="26">
         <v>567</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N8" s="26">
         <v>3</v>
@@ -9269,7 +9217,7 @@
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="104" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B9" s="94"/>
       <c r="C9" s="94"/>
@@ -9289,13 +9237,13 @@
       </c>
       <c r="J9" s="26"/>
       <c r="K9" s="68" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L9" s="69">
         <v>537</v>
       </c>
       <c r="M9" s="68" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N9" s="69">
         <v>3</v>
@@ -9314,20 +9262,20 @@
         <v>629</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I10" s="64">
         <v>3</v>
       </c>
       <c r="J10" s="26"/>
       <c r="K10" s="68" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L10" s="69">
         <v>542</v>
       </c>
       <c r="M10" s="68" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N10" s="69">
         <v>3</v>
@@ -9335,7 +9283,7 @@
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="102" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B11" s="94"/>
       <c r="C11" s="94"/>
@@ -9348,7 +9296,7 @@
         <v>631</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I11" s="26">
         <v>3</v>
@@ -9372,7 +9320,7 @@
         <v>665</v>
       </c>
       <c r="H12" s="68" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I12" s="68">
         <v>3</v>
@@ -9385,7 +9333,7 @@
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="103" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B13" s="94"/>
       <c r="C13" s="94"/>
@@ -9398,7 +9346,7 @@
         <v>770</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I13" s="26">
         <v>3</v>
@@ -9417,7 +9365,7 @@
         <v>692</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D14" s="25">
         <v>2</v>
@@ -9429,10 +9377,10 @@
         <v>139</v>
       </c>
       <c r="B15" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" s="26" t="s">
         <v>268</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>269</v>
       </c>
       <c r="D15" s="25">
         <v>18</v>
@@ -9458,7 +9406,7 @@
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="98" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B17" s="94"/>
       <c r="C17" s="94"/>
@@ -9473,7 +9421,7 @@
         <v>521</v>
       </c>
       <c r="C18" s="63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D18" s="64">
         <v>3</v>
@@ -9488,7 +9436,7 @@
         <v>611</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D19" s="71">
         <v>3</v>
@@ -10504,92 +10452,92 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="75" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="75" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="75" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="75" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="75" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="75" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="75" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="75" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="75" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="75" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="75" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="75" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="75" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="75" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="75" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="75" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="75" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
